--- a/BH-PreVisit-Pellet-Weight-Prep-SMS.xlsx
+++ b/BH-PreVisit-Pellet-Weight-Prep-SMS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -452,13 +452,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hi {patient}, this is a reminder from {hospital} about your upcoming appointment.
-Reply 1 to review details. Reply STOP to opt out.</t>
+          <t>Hi {patient}, this is a reminder from {hospital} about your upcoming appointment.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1 — Review appointment</t>
+          <t>yep I can make Thursday at 10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -470,44 +469,58 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You have an appointment on Thursday at 10:00 AM with Beyond Health in Albuquerque.
-Reply 1 to confirm.
-Reply 2 to cancel.
-Reply 3 to request a reschedule.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1 — Confirm my appointment</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
+          <t>You have an appointment on Thursday at 10:00 AM with Beyond Health in Albuquerque. Can you confirm, or do you need to cancel or reschedule?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>You're confirmed — we look forward to seeing you.
-Prep tip: please arrive 10 minutes early, bring a current medication list, and review any pre-visit instructions your care team shared. For hormone pellet visits, follow your prep guide for the insertion site.
-Questions? Call (505) 899-4414.
-Reply HELP for help. Reply STOP to unsubscribe.</t>
+          <t>You're confirmed. We look forward to seeing you.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A couple prep tips: please arrive 10 minutes early, bring a current medication list, and review any pre-visit instructions your care team shared. For hormone pellet visits, follow your prep guide for the insertion site.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Questions? Call (505) 899-4414. Reply HELP for help. Reply STOP to unsubscribe.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
